--- a/data/trans_orig/DCD-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2012</t>
+          <t>Población con dolor crónico discapacitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110571</t>
+          <t>111932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153367</t>
+          <t>154439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164632</t>
+          <t>166065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216398</t>
+          <t>218939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>628801</t>
+          <t>627222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657506</t>
+          <t>657969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>543683</t>
+          <t>542611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>586479</t>
+          <t>585118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184121</t>
+          <t>1181580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1235887</t>
+          <t>1234454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50870</t>
+          <t>52279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>84065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141564</t>
+          <t>143865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>195077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204999</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262057</t>
+          <t>262292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>932086</t>
+          <t>933882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>967077</t>
+          <t>965668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839652</t>
+          <t>837107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>890620</t>
+          <t>888319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1788074</t>
+          <t>1787839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1845132</t>
+          <t>1845715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55692</t>
+          <t>55978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>94007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135186</t>
+          <t>133205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>133118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>184347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701931</t>
+          <t>701645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>727904</t>
+          <t>728489</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641988</t>
+          <t>643969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>684326</t>
+          <t>683167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1352647</t>
+          <t>1350450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1402643</t>
+          <t>1401679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141008</t>
+          <t>143634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190195</t>
+          <t>193168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200662</t>
+          <t>201445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261017</t>
+          <t>260931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>870308</t>
+          <t>869072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900910</t>
+          <t>900685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>861706</t>
+          <t>858733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>910893</t>
+          <t>908267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1738623</t>
+          <t>1738709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1798978</t>
+          <t>1798195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199449</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>256990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>537033</t>
+          <t>537418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>626371</t>
+          <t>624984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>757863</t>
+          <t>753113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>861259</t>
+          <t>862980</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3166451</t>
+          <t>3169789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3227330</t>
+          <t>3228436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2931938</t>
+          <t>2933325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3021276</t>
+          <t>3020891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6123829</t>
+          <t>6122108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6227225</t>
+          <t>6231975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2016</t>
+          <t>Población con dolor crónico discapacitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62458</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76490</t>
+          <t>75500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111833</t>
+          <t>112362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119321</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163845</t>
+          <t>163503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>612342</t>
+          <t>613322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>640655</t>
+          <t>639258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561006</t>
+          <t>560477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596349</t>
+          <t>597339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1183794</t>
+          <t>1184136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1228318</t>
+          <t>1229570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55667</t>
+          <t>55608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89298</t>
+          <t>87387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109490</t>
+          <t>110136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156372</t>
+          <t>155329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175432</t>
+          <t>175768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>230476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933133</t>
+          <t>935044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966764</t>
+          <t>966823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>886541</t>
+          <t>887584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933423</t>
+          <t>932777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1833438</t>
+          <t>1834868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1889912</t>
+          <t>1889576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>58019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68658</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>102719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106861</t>
+          <t>107926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>152957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>703124</t>
+          <t>701533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>727930</t>
+          <t>727858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682846</t>
+          <t>682292</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>716353</t>
+          <t>717567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1394407</t>
+          <t>1391606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1437702</t>
+          <t>1436637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51673</t>
+          <t>50775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>85287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129309</t>
+          <t>130033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180929</t>
+          <t>178726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192874</t>
+          <t>191940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251374</t>
+          <t>253122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853808</t>
+          <t>852280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885894</t>
+          <t>886792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>862850</t>
+          <t>865053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>914470</t>
+          <t>913746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1729972</t>
+          <t>1728224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1788472</t>
+          <t>1789406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199191</t>
+          <t>199386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260919</t>
+          <t>259359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>422039</t>
+          <t>425440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>505227</t>
+          <t>510224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>639330</t>
+          <t>638683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>743382</t>
+          <t>741169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3133431</t>
+          <t>3134991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3195159</t>
+          <t>3194964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3039315</t>
+          <t>3034318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3122503</t>
+          <t>3119102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6195510</t>
+          <t>6197723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6299562</t>
+          <t>6300209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2023</t>
+          <t>Población con dolor crónico discapacitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79097</t>
+          <t>78355</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112970</t>
+          <t>112483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141135</t>
+          <t>140164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>202029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235650</t>
+          <t>241263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>300685</t>
+          <t>300831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>522471</t>
+          <t>522958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>556344</t>
+          <t>557086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>524479</t>
+          <t>523301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>584195</t>
+          <t>585166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1060087</t>
+          <t>1059941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1125122</t>
+          <t>1119509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151332</t>
+          <t>150467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228613</t>
+          <t>228140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273343</t>
+          <t>272258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241254</t>
+          <t>237905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418962</t>
+          <t>421880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1041532</t>
+          <t>1042397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1129741</t>
+          <t>1141833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>685308</t>
+          <t>686393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>730038</t>
+          <t>730511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1732554</t>
+          <t>1729636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1910262</t>
+          <t>1913611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67314</t>
+          <t>66615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100662</t>
+          <t>101017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111873</t>
+          <t>93851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260545</t>
+          <t>259556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186888</t>
+          <t>187413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>324962</t>
+          <t>328705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604018</t>
+          <t>603663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637366</t>
+          <t>638065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>672821</t>
+          <t>673810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>821493</t>
+          <t>839515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313084</t>
+          <t>1309341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1451158</t>
+          <t>1450633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112633</t>
+          <t>113698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155778</t>
+          <t>153623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222431</t>
+          <t>222758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307799</t>
+          <t>309960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>364171</t>
+          <t>363541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448576</t>
+          <t>446588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771053</t>
+          <t>773208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814198</t>
+          <t>813133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>787133</t>
+          <t>784972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872501</t>
+          <t>872174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1573187</t>
+          <t>1575175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1657592</t>
+          <t>1658222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>337616</t>
+          <t>336018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>477084</t>
+          <t>476740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>736624</t>
+          <t>722617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>976182</t>
+          <t>975036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1154101</t>
+          <t>1138230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1428993</t>
+          <t>1424504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2982733</t>
+          <t>2983077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3122201</t>
+          <t>3123799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2736098</t>
+          <t>2737244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2975656</t>
+          <t>2989663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5743104</t>
+          <t>5747593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6017996</t>
+          <t>6033867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>44073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111932</t>
+          <t>110277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154439</t>
+          <t>151727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166065</t>
+          <t>167376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218939</t>
+          <t>217355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>627222</t>
+          <t>627415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657969</t>
+          <t>659396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542611</t>
+          <t>545323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>585118</t>
+          <t>586773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1181580</t>
+          <t>1183164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1234454</t>
+          <t>1233143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84065</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143865</t>
+          <t>141534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>195077</t>
+          <t>190735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204416</t>
+          <t>207001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262292</t>
+          <t>266232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>933882</t>
+          <t>932134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>965668</t>
+          <t>967113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>837107</t>
+          <t>841449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>888319</t>
+          <t>890650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1787839</t>
+          <t>1783899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1845715</t>
+          <t>1843130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94007</t>
+          <t>96627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133205</t>
+          <t>137367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133118</t>
+          <t>131571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184347</t>
+          <t>181000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701645</t>
+          <t>699653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728489</t>
+          <t>727650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643969</t>
+          <t>639807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>683167</t>
+          <t>680547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1350450</t>
+          <t>1353797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1401679</t>
+          <t>1403226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78667</t>
+          <t>78584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143634</t>
+          <t>145551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193168</t>
+          <t>192475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>201445</t>
+          <t>199094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260931</t>
+          <t>257684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>869072</t>
+          <t>869155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900685</t>
+          <t>900037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>858733</t>
+          <t>859426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>908267</t>
+          <t>906350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1738709</t>
+          <t>1741956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1798195</t>
+          <t>1800546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>198146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>256990</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>537418</t>
+          <t>536814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>624984</t>
+          <t>626754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>753113</t>
+          <t>757979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>862980</t>
+          <t>871047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3169789</t>
+          <t>3169854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3228436</t>
+          <t>3228633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2933325</t>
+          <t>2931555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3020891</t>
+          <t>3021495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6122108</t>
+          <t>6114041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6231975</t>
+          <t>6227109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35542</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>60746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75500</t>
+          <t>74508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112362</t>
+          <t>112408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>119164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163503</t>
+          <t>163647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>613322</t>
+          <t>614054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>639258</t>
+          <t>640292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>560477</t>
+          <t>560431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>597339</t>
+          <t>598331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1184136</t>
+          <t>1183992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1229570</t>
+          <t>1228475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55608</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87387</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110136</t>
+          <t>110701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155329</t>
+          <t>154028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175768</t>
+          <t>173900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>230476</t>
+          <t>232167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>935044</t>
+          <t>934491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966823</t>
+          <t>966969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887584</t>
+          <t>888885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932777</t>
+          <t>932212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1834868</t>
+          <t>1833177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1889576</t>
+          <t>1891444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31694</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102719</t>
+          <t>105106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107926</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152957</t>
+          <t>150490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701533</t>
+          <t>701291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>727858</t>
+          <t>727989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682292</t>
+          <t>679905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>717567</t>
+          <t>715952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1391606</t>
+          <t>1394073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1436637</t>
+          <t>1438877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50775</t>
+          <t>51008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>128960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178726</t>
+          <t>178271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191940</t>
+          <t>193116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253122</t>
+          <t>249781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852280</t>
+          <t>853146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886792</t>
+          <t>886559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>865053</t>
+          <t>865508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>913746</t>
+          <t>914819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1728224</t>
+          <t>1731565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1789406</t>
+          <t>1788230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199386</t>
+          <t>201723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>258952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>425440</t>
+          <t>422673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>510224</t>
+          <t>503963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>638683</t>
+          <t>642058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>741169</t>
+          <t>743100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3134991</t>
+          <t>3135398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3194964</t>
+          <t>3192627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3034318</t>
+          <t>3040579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3119102</t>
+          <t>3121869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6197723</t>
+          <t>6195792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6300209</t>
+          <t>6296834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95102</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78355</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112483</t>
+          <t>120945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>179427</t>
+          <t>193411</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140164</t>
+          <t>176361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202029</t>
+          <t>214774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>274529</t>
+          <t>294474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>241263</t>
+          <t>270489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>300831</t>
+          <t>321824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>540339</t>
+          <t>589647</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>522958</t>
+          <t>569765</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>557086</t>
+          <t>606396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>545903</t>
+          <t>540769</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523301</t>
+          <t>519406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>585166</t>
+          <t>557819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1086243</t>
+          <t>1130415</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1059941</t>
+          <t>1103065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1119509</t>
+          <t>1154400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>112307</t>
+          <t>119330</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51031</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150467</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>250806</t>
+          <t>277663</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228140</t>
+          <t>252738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272258</t>
+          <t>303874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>363113</t>
+          <t>396994</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>237905</t>
+          <t>365889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>421880</t>
+          <t>431962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1080557</t>
+          <t>929587</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1042397</t>
+          <t>906610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141833</t>
+          <t>948238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>707845</t>
+          <t>793811</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686393</t>
+          <t>767600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>730511</t>
+          <t>818736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1788403</t>
+          <t>1723397</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1729636</t>
+          <t>1688429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1913611</t>
+          <t>1754502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>95024</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>77507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101017</t>
+          <t>114107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>193052</t>
+          <t>225050</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93851</t>
+          <t>200902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259556</t>
+          <t>248956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>276224</t>
+          <t>320074</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187413</t>
+          <t>288985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>328705</t>
+          <t>349270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621507</t>
+          <t>708049</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603663</t>
+          <t>688966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638065</t>
+          <t>725566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>740314</t>
+          <t>587209</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673810</t>
+          <t>563303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>839515</t>
+          <t>611357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1361822</t>
+          <t>1295258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309341</t>
+          <t>1266062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1450633</t>
+          <t>1326347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>139493</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113698</t>
+          <t>119081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153623</t>
+          <t>161815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>276668</t>
+          <t>301786</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>277593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>309960</t>
+          <t>329419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>410131</t>
+          <t>441279</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363541</t>
+          <t>408434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446588</t>
+          <t>476477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>793368</t>
+          <t>850569</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773208</t>
+          <t>828247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813133</t>
+          <t>870981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>818264</t>
+          <t>817255</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>784972</t>
+          <t>789622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872174</t>
+          <t>841448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1611632</t>
+          <t>1667825</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1575175</t>
+          <t>1632627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1658222</t>
+          <t>1700670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>336018</t>
+          <t>418162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>476740</t>
+          <t>503157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>899952</t>
+          <t>997910</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>722617</t>
+          <t>952398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>1048222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1323997</t>
+          <t>1452821</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1138230</t>
+          <t>1385950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1424504</t>
+          <t>1517258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3035772</t>
+          <t>3077851</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2983077</t>
+          <t>3029605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3123799</t>
+          <t>3114600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2812328</t>
+          <t>2739044</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2737244</t>
+          <t>2688732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2989663</t>
+          <t>2784556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5848100</t>
+          <t>5816895</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5747593</t>
+          <t>5752458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6033867</t>
+          <t>5883766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
